--- a/src/width_txt/Максимальные_значения_фильтра_Гилберта_АЦП_№3.xlsx
+++ b/src/width_txt/Максимальные_значения_фильтра_Гилберта_АЦП_№3.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="760" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1064" uniqueCount="76">
   <si>
     <t>Row</t>
   </si>
@@ -335,7 +335,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="0">
-        <v>3417371036</v>
+        <v>2322089732</v>
       </c>
     </row>
     <row r="5">
@@ -343,10 +343,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>3417371036</v>
+        <v>2322089732</v>
       </c>
       <c r="C5" s="0">
-        <v>3417371036</v>
+        <v>2322089732</v>
       </c>
     </row>
     <row r="6">
@@ -357,7 +357,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="0">
-        <v>11961778268</v>
+        <v>8639121884</v>
       </c>
     </row>
     <row r="7">
@@ -365,10 +365,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>10252113108</v>
+        <v>6966269196</v>
       </c>
       <c r="C7" s="0">
-        <v>11961778268</v>
+        <v>8639121884</v>
       </c>
     </row>
     <row r="8">
@@ -379,7 +379,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="0">
-        <v>30567394473</v>
+        <v>22156529163</v>
       </c>
     </row>
     <row r="9">
@@ -387,10 +387,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>23067254493</v>
+        <v>15674105691</v>
       </c>
       <c r="C9" s="0">
-        <v>30567394473</v>
+        <v>22156529163</v>
       </c>
     </row>
     <row r="10">
@@ -401,7 +401,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="0">
-        <v>64856418079</v>
+        <v>46633552291</v>
       </c>
     </row>
     <row r="11">
@@ -409,10 +409,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>43571480709</v>
+        <v>29606644083</v>
       </c>
       <c r="C11" s="0">
-        <v>64856418079</v>
+        <v>46633552291</v>
       </c>
     </row>
     <row r="12">
@@ -423,7 +423,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="0">
-        <v>121097458257</v>
+        <v>87590025120</v>
       </c>
     </row>
     <row r="13">
@@ -431,10 +431,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>75182162792</v>
+        <v>51085974104</v>
       </c>
       <c r="C13" s="0">
-        <v>121097458257</v>
+        <v>87590025120</v>
       </c>
     </row>
     <row r="14">
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="C14" s="0">
-        <v>207781743862</v>
+        <v>152548209462</v>
       </c>
     </row>
     <row r="15">
@@ -453,10 +453,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>122171014537</v>
+        <v>83014707919</v>
       </c>
       <c r="C15" s="0">
-        <v>207781743862</v>
+        <v>152548209462</v>
       </c>
     </row>
     <row r="16">
@@ -467,7 +467,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="0">
-        <v>331989410001</v>
+        <v>250170102523</v>
       </c>
     </row>
     <row r="17">
@@ -475,10 +475,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>187955406980</v>
+        <v>127714935260</v>
       </c>
       <c r="C17" s="0">
-        <v>331989410001</v>
+        <v>250170102523</v>
       </c>
     </row>
     <row r="18">
@@ -489,7 +489,7 @@
         <v>0</v>
       </c>
       <c r="C18" s="0">
-        <v>504925372592</v>
+        <v>392618774561</v>
       </c>
     </row>
     <row r="19">
@@ -497,10 +497,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>279370082193</v>
+        <v>189830835591</v>
       </c>
       <c r="C19" s="0">
-        <v>504925372592</v>
+        <v>392618774561</v>
       </c>
     </row>
     <row r="20">
@@ -511,7 +511,7 @@
         <v>0</v>
       </c>
       <c r="C20" s="0">
-        <v>742060872060</v>
+        <v>594884275894</v>
       </c>
     </row>
     <row r="21">
@@ -519,10 +519,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>403249782248</v>
+        <v>274006588376</v>
       </c>
       <c r="C21" s="0">
-        <v>742060872060</v>
+        <v>594884275894</v>
       </c>
     </row>
     <row r="22">
@@ -533,7 +533,7 @@
         <v>0</v>
       </c>
       <c r="C22" s="0">
-        <v>1064272967879</v>
+        <v>877452019697</v>
       </c>
     </row>
     <row r="23">
@@ -541,10 +541,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>570700963012</v>
+        <v>387788985244</v>
       </c>
       <c r="C23" s="0">
-        <v>1064272967879</v>
+        <v>877452019697</v>
       </c>
     </row>
     <row r="24">
@@ -555,7 +555,7 @@
         <v>0</v>
       </c>
       <c r="C24" s="0">
-        <v>1499513086888</v>
+        <v>1267094813794</v>
       </c>
     </row>
     <row r="25">
@@ -563,10 +563,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>795393108629</v>
+        <v>540466385123</v>
       </c>
       <c r="C25" s="0">
-        <v>1499513086888</v>
+        <v>1267094813794</v>
       </c>
     </row>
     <row r="26">
@@ -577,7 +577,7 @@
         <v>0</v>
       </c>
       <c r="C26" s="0">
-        <v>2089706394447</v>
+        <v>1802416708436</v>
       </c>
     </row>
     <row r="27">
@@ -585,10 +585,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>1100393473592</v>
+        <v>747712893704</v>
       </c>
       <c r="C27" s="0">
-        <v>2089706394447</v>
+        <v>1802416708436</v>
       </c>
     </row>
     <row r="28">
@@ -599,7 +599,7 @@
         <v>0</v>
       </c>
       <c r="C28" s="0">
-        <v>2909182087271</v>
+        <v>2547368871415</v>
       </c>
     </row>
     <row r="29">
@@ -607,10 +607,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>1531836566887</v>
+        <v>1040876722369</v>
       </c>
       <c r="C29" s="0">
-        <v>2909182087271</v>
+        <v>2547368871415</v>
       </c>
     </row>
     <row r="30">
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="C30" s="0">
-        <v>4100564723927</v>
+        <v>3617402755967</v>
       </c>
     </row>
     <row r="31">
@@ -629,10 +629,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>2181991406486</v>
+        <v>1482654293882</v>
       </c>
       <c r="C31" s="0">
-        <v>4100564723927</v>
+        <v>3617402755967</v>
       </c>
     </row>
     <row r="32">
@@ -643,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="C32" s="0">
-        <v>6001205193184</v>
+        <v>5272133627495</v>
       </c>
     </row>
     <row r="33">
@@ -651,10 +651,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>3295200021463</v>
+        <v>2239075024081</v>
       </c>
       <c r="C33" s="0">
-        <v>6001205193184</v>
+        <v>5272133627495</v>
       </c>
     </row>
     <row r="34">
@@ -665,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="C34" s="0">
-        <v>9735602382612</v>
+        <v>8331221537797</v>
       </c>
     </row>
     <row r="35">
@@ -673,10 +673,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>5776211393599</v>
+        <v>3924912169513</v>
       </c>
       <c r="C35" s="0">
-        <v>9735602382612</v>
+        <v>8331221537797</v>
       </c>
     </row>
     <row r="36">
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="C36" s="0">
-        <v>24131496591784</v>
+        <v>18954808109691</v>
       </c>
     </row>
     <row r="37">
@@ -695,10 +695,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>17766912016164</v>
+        <v>12072544516668</v>
       </c>
       <c r="C37" s="0">
-        <v>24131496591784</v>
+        <v>18954808109691</v>
       </c>
     </row>
     <row r="38">
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="C38" s="0">
-        <v>29715712767741</v>
+        <v>15406849382283</v>
       </c>
     </row>
     <row r="39">
@@ -717,10 +717,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="0">
-        <v>17766912016164</v>
+        <v>12072544516668</v>
       </c>
       <c r="C39" s="0">
-        <v>29715712767741</v>
+        <v>15406849382283</v>
       </c>
     </row>
     <row r="40">
@@ -731,7 +731,7 @@
         <v>0</v>
       </c>
       <c r="C40" s="0">
-        <v>32578358766290</v>
+        <v>14678144745683</v>
       </c>
     </row>
     <row r="41">
@@ -739,10 +739,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="0">
-        <v>5776211393599</v>
+        <v>3924912169513</v>
       </c>
       <c r="C41" s="0">
-        <v>32578358766290</v>
+        <v>14678144745683</v>
       </c>
     </row>
     <row r="42">
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="C42" s="0">
-        <v>33912248221168</v>
+        <v>14393297257695</v>
       </c>
     </row>
     <row r="43">
@@ -761,10 +761,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="0">
-        <v>3295200021463</v>
+        <v>2239075024081</v>
       </c>
       <c r="C43" s="0">
-        <v>33912248221168</v>
+        <v>14393297257695</v>
       </c>
     </row>
     <row r="44">
@@ -775,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="C44" s="0">
-        <v>35073306405542</v>
+        <v>14261066053055</v>
       </c>
     </row>
     <row r="45">
@@ -783,10 +783,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="0">
-        <v>2181991406486</v>
+        <v>1482654293882</v>
       </c>
       <c r="C45" s="0">
-        <v>35073306405542</v>
+        <v>14261066053055</v>
       </c>
     </row>
     <row r="46">
@@ -797,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="C46" s="0">
-        <v>34654919383544</v>
+        <v>14195836298872</v>
       </c>
     </row>
     <row r="47">
@@ -805,10 +805,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="0">
-        <v>1531836566887</v>
+        <v>1040876722369</v>
       </c>
       <c r="C47" s="0">
-        <v>34654919383544</v>
+        <v>14195836298872</v>
       </c>
     </row>
     <row r="48">
@@ -819,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="C48" s="0">
-        <v>34068579834562</v>
+        <v>14163191086216</v>
       </c>
     </row>
     <row r="49">
@@ -827,10 +827,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="0">
-        <v>1100393473592</v>
+        <v>747712893704</v>
       </c>
       <c r="C49" s="0">
-        <v>34068579834562</v>
+        <v>14163191086216</v>
       </c>
     </row>
     <row r="50">
@@ -841,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="C50" s="0">
-        <v>33882787125649</v>
+        <v>14147010305285</v>
       </c>
     </row>
     <row r="51">
@@ -849,10 +849,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="0">
-        <v>795393108629</v>
+        <v>540466385123</v>
       </c>
       <c r="C51" s="0">
-        <v>33882787125649</v>
+        <v>14147010305285</v>
       </c>
     </row>
     <row r="52">
@@ -863,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="C52" s="0">
-        <v>33516734485657</v>
+        <v>14139223913585</v>
       </c>
     </row>
     <row r="53">
@@ -871,10 +871,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="0">
-        <v>570700963012</v>
+        <v>387788985244</v>
       </c>
       <c r="C53" s="0">
-        <v>33516734485657</v>
+        <v>14139223913585</v>
       </c>
     </row>
     <row r="54">
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="C54" s="0">
-        <v>33250476408345</v>
+        <v>14135636937313</v>
       </c>
     </row>
     <row r="55">
@@ -893,10 +893,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="0">
-        <v>403249782248</v>
+        <v>274006588376</v>
       </c>
       <c r="C55" s="0">
-        <v>33250476408345</v>
+        <v>14135636937313</v>
       </c>
     </row>
     <row r="56">
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="C56" s="0">
-        <v>33291841450419</v>
+        <v>14134073054908</v>
       </c>
     </row>
     <row r="57">
@@ -915,10 +915,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="0">
-        <v>279370082193</v>
+        <v>189830835591</v>
       </c>
       <c r="C57" s="0">
-        <v>33291841450419</v>
+        <v>14134073054908</v>
       </c>
     </row>
     <row r="58">
@@ -929,7 +929,7 @@
         <v>0</v>
       </c>
       <c r="C58" s="0">
-        <v>33365147399179</v>
+        <v>14133439590428</v>
       </c>
     </row>
     <row r="59">
@@ -937,10 +937,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="0">
-        <v>187955406980</v>
+        <v>127714935260</v>
       </c>
       <c r="C59" s="0">
-        <v>33365147399179</v>
+        <v>14133439590428</v>
       </c>
     </row>
     <row r="60">
@@ -951,7 +951,7 @@
         <v>0</v>
       </c>
       <c r="C60" s="0">
-        <v>33405433082617</v>
+        <v>14133205543901</v>
       </c>
     </row>
     <row r="61">
@@ -959,10 +959,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="0">
-        <v>122171014537</v>
+        <v>83014707919</v>
       </c>
       <c r="C61" s="0">
-        <v>33405433082617</v>
+        <v>14133205543901</v>
       </c>
     </row>
     <row r="62">
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="C62" s="0">
-        <v>33466207556553</v>
+        <v>14133129704533</v>
       </c>
     </row>
     <row r="63">
@@ -981,10 +981,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="0">
-        <v>75182162792</v>
+        <v>51085974104</v>
       </c>
       <c r="C63" s="0">
-        <v>33466207556553</v>
+        <v>14133129704533</v>
       </c>
     </row>
     <row r="64">
@@ -995,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="C64" s="0">
-        <v>33447275677794</v>
+        <v>14133109020463</v>
       </c>
     </row>
     <row r="65">
@@ -1003,10 +1003,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="0">
-        <v>43571480709</v>
+        <v>29606644083</v>
       </c>
       <c r="C65" s="0">
-        <v>33447275677794</v>
+        <v>14133109020463</v>
       </c>
     </row>
     <row r="66">
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="C66" s="0">
-        <v>33457085559795</v>
+        <v>14133104679268</v>
       </c>
     </row>
     <row r="67">
@@ -1025,10 +1025,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="0">
-        <v>23067254493</v>
+        <v>15674105691</v>
       </c>
       <c r="C67" s="0">
-        <v>33457085559795</v>
+        <v>14133104679268</v>
       </c>
     </row>
     <row r="68">
@@ -1039,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="C68" s="0">
-        <v>33450851912079</v>
+        <v>14133104123008</v>
       </c>
     </row>
     <row r="69">
@@ -1047,10 +1047,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="0">
-        <v>10252113108</v>
+        <v>6966269196</v>
       </c>
       <c r="C69" s="0">
-        <v>33450851912079</v>
+        <v>14133104123008</v>
       </c>
     </row>
     <row r="70">
@@ -1061,7 +1061,7 @@
         <v>0</v>
       </c>
       <c r="C70" s="0">
-        <v>33448797184767</v>
+        <v>14133104094032</v>
       </c>
     </row>
     <row r="71">
@@ -1069,10 +1069,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="0">
-        <v>3417371036</v>
+        <v>2322089732</v>
       </c>
       <c r="C71" s="0">
-        <v>33448797184767</v>
+        <v>14133104094032</v>
       </c>
     </row>
     <row r="72">
@@ -1083,7 +1083,7 @@
         <v>0</v>
       </c>
       <c r="C72" s="0">
-        <v>33448797184767</v>
+        <v>14133104094032</v>
       </c>
     </row>
     <row r="73">
@@ -1094,7 +1094,7 @@
         <v>0</v>
       </c>
       <c r="C73" s="0">
-        <v>33448797184767</v>
+        <v>14133104094032</v>
       </c>
     </row>
     <row r="74">

--- a/src/width_txt/Максимальные_значения_фильтра_Гилберта_АЦП_№3.xlsx
+++ b/src/width_txt/Максимальные_значения_фильтра_Гилберта_АЦП_№3.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1064" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="4261" uniqueCount="77">
   <si>
     <t>Row</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>Adders_hilbert</t>
+  </si>
+  <si>
+    <t>y_Hilbert_outInt</t>
   </si>
 </sst>
 </file>
@@ -286,12 +289,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="true"/>
     <col min="2" max="2" width="17.85546875" customWidth="true"/>
-    <col min="3" max="3" width="15.85546875" customWidth="true"/>
+    <col min="3" max="3" width="14.42578125" customWidth="true"/>
+    <col min="4" max="4" width="15.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -304,6 +308,9 @@
       <c r="C1" s="0" t="s">
         <v>75</v>
       </c>
+      <c r="D1" s="0" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -315,6 +322,9 @@
       <c r="C2" s="0">
         <v>0</v>
       </c>
+      <c r="D2" s="0">
+        <v>2066</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
@@ -326,6 +336,9 @@
       <c r="C3" s="0">
         <v>0</v>
       </c>
+      <c r="D3" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
@@ -335,7 +348,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="0">
-        <v>2322089732</v>
+        <v>6471</v>
+      </c>
+      <c r="D4" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -343,10 +359,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>2322089732</v>
+        <v>6471</v>
       </c>
       <c r="C5" s="0">
-        <v>2322089732</v>
+        <v>6471</v>
+      </c>
+      <c r="D5" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -354,10 +373,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>0</v>
+        <v>2157</v>
       </c>
       <c r="C6" s="0">
-        <v>8639121884</v>
+        <v>21849</v>
+      </c>
+      <c r="D6" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -365,10 +387,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>6966269196</v>
+        <v>19413</v>
       </c>
       <c r="C7" s="0">
-        <v>8639121884</v>
+        <v>25299</v>
+      </c>
+      <c r="D7" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -376,10 +401,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>0</v>
+        <v>4314</v>
       </c>
       <c r="C8" s="0">
-        <v>22156529163</v>
+        <v>56679</v>
+      </c>
+      <c r="D8" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -387,10 +415,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>15674105691</v>
+        <v>36669</v>
       </c>
       <c r="C9" s="0">
-        <v>22156529163</v>
+        <v>85355</v>
+      </c>
+      <c r="D9" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -398,10 +429,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>0</v>
+        <v>34512</v>
       </c>
       <c r="C10" s="0">
-        <v>46633552291</v>
+        <v>117028</v>
+      </c>
+      <c r="D10" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -409,10 +443,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>29606644083</v>
+        <v>40983</v>
       </c>
       <c r="C11" s="0">
-        <v>46633552291</v>
+        <v>201619</v>
+      </c>
+      <c r="D11" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -420,10 +457,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>0</v>
+        <v>107850</v>
       </c>
       <c r="C12" s="0">
-        <v>87590025120</v>
+        <v>223290</v>
+      </c>
+      <c r="D12" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -431,10 +471,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>51085974104</v>
+        <v>28041</v>
       </c>
       <c r="C13" s="0">
-        <v>87590025120</v>
+        <v>386312</v>
+      </c>
+      <c r="D13" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -442,10 +485,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>0</v>
+        <v>228642</v>
       </c>
       <c r="C14" s="0">
-        <v>152548209462</v>
+        <v>385097</v>
+      </c>
+      <c r="D14" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -453,10 +499,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>83014707919</v>
+        <v>2157</v>
       </c>
       <c r="C15" s="0">
-        <v>152548209462</v>
+        <v>627619</v>
+      </c>
+      <c r="D15" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -464,10 +513,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>0</v>
+        <v>371004</v>
       </c>
       <c r="C16" s="0">
-        <v>250170102523</v>
+        <v>619233</v>
+      </c>
+      <c r="D16" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -475,10 +527,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>127714935260</v>
+        <v>15099</v>
       </c>
       <c r="C17" s="0">
-        <v>250170102523</v>
+        <v>884249</v>
+      </c>
+      <c r="D17" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -486,10 +541,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>0</v>
+        <v>470226</v>
       </c>
       <c r="C18" s="0">
-        <v>392618774561</v>
+        <v>907011</v>
+      </c>
+      <c r="D18" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -497,10 +555,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>189830835591</v>
+        <v>40983</v>
       </c>
       <c r="C19" s="0">
-        <v>392618774561</v>
+        <v>1134643</v>
+      </c>
+      <c r="D19" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -508,10 +569,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>0</v>
+        <v>427086</v>
       </c>
       <c r="C20" s="0">
-        <v>594884275894</v>
+        <v>1209800</v>
+      </c>
+      <c r="D20" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -519,10 +583,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>274006588376</v>
+        <v>224328</v>
       </c>
       <c r="C21" s="0">
-        <v>594884275894</v>
+        <v>1290066</v>
+      </c>
+      <c r="D21" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -530,10 +597,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>0</v>
+        <v>144519</v>
       </c>
       <c r="C22" s="0">
-        <v>877452019697</v>
+        <v>1450461</v>
+      </c>
+      <c r="D22" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -541,10 +611,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>387788985244</v>
+        <v>550035</v>
       </c>
       <c r="C23" s="0">
-        <v>877452019697</v>
+        <v>1450657</v>
+      </c>
+      <c r="D23" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -552,10 +625,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>0</v>
+        <v>422772</v>
       </c>
       <c r="C24" s="0">
-        <v>1267094813794</v>
+        <v>1472772</v>
+      </c>
+      <c r="D24" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -563,10 +639,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>540466385123</v>
+        <v>927510</v>
       </c>
       <c r="C25" s="0">
-        <v>1267094813794</v>
+        <v>1856922</v>
+      </c>
+      <c r="D25" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -574,10 +653,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>0</v>
+        <v>1218705</v>
       </c>
       <c r="C26" s="0">
-        <v>1802416708436</v>
+        <v>1740285</v>
+      </c>
+      <c r="D26" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -585,10 +667,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>747712893704</v>
+        <v>1128111</v>
       </c>
       <c r="C27" s="0">
-        <v>1802416708436</v>
+        <v>2983248</v>
+      </c>
+      <c r="D27" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -596,10 +681,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>0</v>
+        <v>2062092</v>
       </c>
       <c r="C28" s="0">
-        <v>2547368871415</v>
+        <v>2983248</v>
+      </c>
+      <c r="D28" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -607,10 +695,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>1040876722369</v>
+        <v>776520</v>
       </c>
       <c r="C29" s="0">
-        <v>2547368871415</v>
+        <v>4535513</v>
+      </c>
+      <c r="D29" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -618,10 +709,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>0</v>
+        <v>2696250</v>
       </c>
       <c r="C30" s="0">
-        <v>3617402755967</v>
+        <v>5041142</v>
+      </c>
+      <c r="D30" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -629,10 +723,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>1482654293882</v>
+        <v>662199</v>
       </c>
       <c r="C31" s="0">
-        <v>3617402755967</v>
+        <v>7311599</v>
+      </c>
+      <c r="D31" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -640,10 +737,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>0</v>
+        <v>2860182</v>
       </c>
       <c r="C32" s="0">
-        <v>5272133627495</v>
+        <v>10378313</v>
+      </c>
+      <c r="D32" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -651,10 +751,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>2239075024081</v>
+        <v>4016334</v>
       </c>
       <c r="C33" s="0">
-        <v>5272133627495</v>
+        <v>11989131</v>
+      </c>
+      <c r="D33" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -662,10 +765,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>0</v>
+        <v>2409369</v>
       </c>
       <c r="C34" s="0">
-        <v>8331221537797</v>
+        <v>20197622</v>
+      </c>
+      <c r="D34" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -673,10 +779,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>3924912169513</v>
+        <v>11600346</v>
       </c>
       <c r="C35" s="0">
-        <v>8331221537797</v>
+        <v>20962422</v>
+      </c>
+      <c r="D35" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -684,10 +793,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>0</v>
+        <v>1380480</v>
       </c>
       <c r="C36" s="0">
-        <v>18954808109691</v>
+        <v>55096003</v>
+      </c>
+      <c r="D36" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -695,10 +807,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>12072544516668</v>
+        <v>43789257</v>
       </c>
       <c r="C37" s="0">
-        <v>18954808109691</v>
+        <v>55096003</v>
+      </c>
+      <c r="D37" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -709,7 +824,10 @@
         <v>0</v>
       </c>
       <c r="C38" s="0">
-        <v>15406849382283</v>
+        <v>60726903</v>
+      </c>
+      <c r="D38" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -717,10 +835,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="0">
-        <v>12072544516668</v>
+        <v>43789257</v>
       </c>
       <c r="C39" s="0">
-        <v>15406849382283</v>
+        <v>62036343</v>
+      </c>
+      <c r="D39" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -728,10 +849,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="0">
-        <v>0</v>
+        <v>1380480</v>
       </c>
       <c r="C40" s="0">
-        <v>14678144745683</v>
+        <v>70947689</v>
+      </c>
+      <c r="D40" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -739,10 +863,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="0">
-        <v>3924912169513</v>
+        <v>11600346</v>
       </c>
       <c r="C41" s="0">
-        <v>14678144745683</v>
+        <v>71655867</v>
+      </c>
+      <c r="D41" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -750,10 +877,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="0">
-        <v>0</v>
+        <v>2409369</v>
       </c>
       <c r="C42" s="0">
-        <v>14393297257695</v>
+        <v>71276989</v>
+      </c>
+      <c r="D42" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -761,10 +891,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="0">
-        <v>2239075024081</v>
+        <v>4016334</v>
       </c>
       <c r="C43" s="0">
-        <v>14393297257695</v>
+        <v>70437631</v>
+      </c>
+      <c r="D43" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -772,10 +905,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="0">
-        <v>0</v>
+        <v>2860182</v>
       </c>
       <c r="C44" s="0">
-        <v>14261066053055</v>
+        <v>69929239</v>
+      </c>
+      <c r="D44" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -783,10 +919,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="0">
-        <v>1482654293882</v>
+        <v>662199</v>
       </c>
       <c r="C45" s="0">
-        <v>14261066053055</v>
+        <v>67367989</v>
+      </c>
+      <c r="D45" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -794,10 +933,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="0">
-        <v>0</v>
+        <v>2696250</v>
       </c>
       <c r="C46" s="0">
-        <v>14195836298872</v>
+        <v>67964509</v>
+      </c>
+      <c r="D46" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -805,10 +947,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="0">
-        <v>1040876722369</v>
+        <v>776520</v>
       </c>
       <c r="C47" s="0">
-        <v>14195836298872</v>
+        <v>67360317</v>
+      </c>
+      <c r="D47" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -816,10 +961,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="0">
-        <v>0</v>
+        <v>2062092</v>
       </c>
       <c r="C48" s="0">
-        <v>14163191086216</v>
+        <v>67029258</v>
+      </c>
+      <c r="D48" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -827,10 +975,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="0">
-        <v>747712893704</v>
+        <v>1128111</v>
       </c>
       <c r="C49" s="0">
-        <v>14163191086216</v>
+        <v>67966028</v>
+      </c>
+      <c r="D49" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -838,10 +989,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="0">
-        <v>0</v>
+        <v>1218705</v>
       </c>
       <c r="C50" s="0">
-        <v>14147010305285</v>
+        <v>67085818</v>
+      </c>
+      <c r="D50" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -849,10 +1003,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="0">
-        <v>540466385123</v>
+        <v>927510</v>
       </c>
       <c r="C51" s="0">
-        <v>14147010305285</v>
+        <v>67410394</v>
+      </c>
+      <c r="D51" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -860,10 +1017,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="0">
-        <v>0</v>
+        <v>422772</v>
       </c>
       <c r="C52" s="0">
-        <v>14139223913585</v>
+        <v>67249234</v>
+      </c>
+      <c r="D52" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -871,10 +1031,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="0">
-        <v>387788985244</v>
+        <v>550035</v>
       </c>
       <c r="C53" s="0">
-        <v>14139223913585</v>
+        <v>67291645</v>
+      </c>
+      <c r="D53" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -882,10 +1045,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="0">
-        <v>0</v>
+        <v>144519</v>
       </c>
       <c r="C54" s="0">
-        <v>14135636937313</v>
+        <v>67463869</v>
+      </c>
+      <c r="D54" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -893,10 +1059,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="0">
-        <v>274006588376</v>
+        <v>224328</v>
       </c>
       <c r="C55" s="0">
-        <v>14135636937313</v>
+        <v>67869571</v>
+      </c>
+      <c r="D55" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -904,10 +1073,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="0">
-        <v>0</v>
+        <v>427086</v>
       </c>
       <c r="C56" s="0">
-        <v>14134073054908</v>
+        <v>67901035</v>
+      </c>
+      <c r="D56" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -915,10 +1087,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="0">
-        <v>189830835591</v>
+        <v>40983</v>
       </c>
       <c r="C57" s="0">
-        <v>14134073054908</v>
+        <v>68038811</v>
+      </c>
+      <c r="D57" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -926,10 +1101,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="0">
-        <v>0</v>
+        <v>470226</v>
       </c>
       <c r="C58" s="0">
-        <v>14133439590428</v>
+        <v>68043235</v>
+      </c>
+      <c r="D58" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -937,10 +1115,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="0">
-        <v>127714935260</v>
+        <v>15099</v>
       </c>
       <c r="C59" s="0">
-        <v>14133439590428</v>
+        <v>67758231</v>
+      </c>
+      <c r="D59" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -948,10 +1129,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="0">
-        <v>0</v>
+        <v>371004</v>
       </c>
       <c r="C60" s="0">
-        <v>14133205543901</v>
+        <v>67760278</v>
+      </c>
+      <c r="D60" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -959,10 +1143,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="0">
-        <v>83014707919</v>
+        <v>2157</v>
       </c>
       <c r="C61" s="0">
-        <v>14133205543901</v>
+        <v>67584636</v>
+      </c>
+      <c r="D61" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -970,10 +1157,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="0">
-        <v>0</v>
+        <v>228642</v>
       </c>
       <c r="C62" s="0">
-        <v>14133129704533</v>
+        <v>67576407</v>
+      </c>
+      <c r="D62" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -981,10 +1171,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="0">
-        <v>51085974104</v>
+        <v>28041</v>
       </c>
       <c r="C63" s="0">
-        <v>14133129704533</v>
+        <v>67608057</v>
+      </c>
+      <c r="D63" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -992,10 +1185,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="0">
-        <v>0</v>
+        <v>107850</v>
       </c>
       <c r="C64" s="0">
-        <v>14133109020463</v>
+        <v>67639521</v>
+      </c>
+      <c r="D64" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1003,10 +1199,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="0">
-        <v>29606644083</v>
+        <v>40983</v>
       </c>
       <c r="C65" s="0">
-        <v>14133109020463</v>
+        <v>67672305</v>
+      </c>
+      <c r="D65" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1014,10 +1213,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="0">
-        <v>0</v>
+        <v>34512</v>
       </c>
       <c r="C66" s="0">
-        <v>14133104679268</v>
+        <v>67700491</v>
+      </c>
+      <c r="D66" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1025,10 +1227,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="0">
-        <v>15674105691</v>
+        <v>36669</v>
       </c>
       <c r="C67" s="0">
-        <v>14133104679268</v>
+        <v>67701755</v>
+      </c>
+      <c r="D67" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1036,10 +1241,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="0">
-        <v>0</v>
+        <v>4314</v>
       </c>
       <c r="C68" s="0">
-        <v>14133104123008</v>
+        <v>67696049</v>
+      </c>
+      <c r="D68" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -1047,10 +1255,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="0">
-        <v>6966269196</v>
+        <v>19413</v>
       </c>
       <c r="C69" s="0">
-        <v>14133104123008</v>
+        <v>67697707</v>
+      </c>
+      <c r="D69" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1058,10 +1269,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="0">
-        <v>0</v>
+        <v>2157</v>
       </c>
       <c r="C70" s="0">
-        <v>14133104094032</v>
+        <v>67691563</v>
+      </c>
+      <c r="D70" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1069,10 +1283,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="0">
-        <v>2322089732</v>
+        <v>6471</v>
       </c>
       <c r="C71" s="0">
-        <v>14133104094032</v>
+        <v>67691563</v>
+      </c>
+      <c r="D71" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1083,7 +1300,10 @@
         <v>0</v>
       </c>
       <c r="C72" s="0">
-        <v>14133104094032</v>
+        <v>67691563</v>
+      </c>
+      <c r="D72" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1094,7 +1314,10 @@
         <v>0</v>
       </c>
       <c r="C73" s="0">
-        <v>14133104094032</v>
+        <v>67691563</v>
+      </c>
+      <c r="D73" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1107,6 +1330,9 @@
       <c r="C74" s="0">
         <v>0</v>
       </c>
+      <c r="D74" s="0">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>
